--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T08:17:27+00:00</t>
+    <t>2023-11-21T14:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T14:08:22+00:00</t>
+    <t>2023-11-21T15:06:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T15:06:57+00:00</t>
+    <t>2023-11-21T15:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T15:46:53+00:00</t>
+    <t>2023-11-21T16:01:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T16:01:46+00:00</t>
+    <t>2023-11-21T16:06:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T16:06:52+00:00</t>
+    <t>2023-11-22T15:35:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:35:46+00:00</t>
+    <t>2023-11-22T15:45:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:45:36+00:00</t>
+    <t>2023-11-22T15:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T15:47:55+00:00</t>
+    <t>2023-11-22T16:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T16:02:35+00:00</t>
+    <t>2023-11-22T16:24:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-22T16:24:01+00:00</t>
+    <t>2023-11-24T09:28:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-24T09:28:27+00:00</t>
+    <t>2023-11-29T07:54:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T07:54:05+00:00</t>
+    <t>2023-12-13T14:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/epd/StructureDefinition-tddui-bundle.xlsx
+++ b/ig/epd/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T14:14:48+00:00</t>
+    <t>2023-12-13T15:28:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6853,7 +6853,7 @@
         <v>87</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
